--- a/ECO_STRUCT_Datos.xlsx
+++ b/ECO_STRUCT_Datos.xlsx
@@ -1548,7 +1548,7 @@
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>452000</v>
+        <v>451635.85</v>
       </c>
       <c r="D7" s="6">
         <f>C7/C24</f>
@@ -17654,7 +17654,7 @@
         </is>
       </c>
       <c r="B21" s="6" t="n">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>20</v>
@@ -17868,7 +17868,7 @@
         </is>
       </c>
       <c r="B30" s="6" t="n">
-        <v>3970</v>
+        <v>3960</v>
       </c>
       <c r="C30" s="4" t="n">
         <v>20</v>

--- a/ECO_STRUCT_Datos.xlsx
+++ b/ECO_STRUCT_Datos.xlsx
@@ -568,7 +568,7 @@
         </is>
       </c>
       <c r="B8" s="4">
-        <f>'Mano de Obra'!D32</f>
+        <f>'Mano de Obra'!D28</f>
         <v/>
       </c>
     </row>
@@ -17206,7 +17206,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -17283,7 +17283,7 @@
         <v>2026</v>
       </c>
       <c r="F5" s="6">
-        <f>D5/D32</f>
+        <f>D5/D28</f>
         <v/>
       </c>
     </row>
@@ -17307,7 +17307,7 @@
         <v>2026</v>
       </c>
       <c r="F6" s="6">
-        <f>D6/D32</f>
+        <f>D6/D28</f>
         <v/>
       </c>
     </row>
@@ -17331,7 +17331,7 @@
         <v>2026</v>
       </c>
       <c r="F7" s="6">
-        <f>D7/D32</f>
+        <f>D7/D28</f>
         <v/>
       </c>
     </row>
@@ -17355,7 +17355,7 @@
         <v>2026</v>
       </c>
       <c r="F8" s="6">
-        <f>D8/D32</f>
+        <f>D8/D28</f>
         <v/>
       </c>
     </row>
@@ -17379,7 +17379,7 @@
         <v>2026</v>
       </c>
       <c r="F9" s="6">
-        <f>D9/D32</f>
+        <f>D9/D28</f>
         <v/>
       </c>
     </row>
@@ -17403,7 +17403,7 @@
         <v>2026</v>
       </c>
       <c r="F10" s="6">
-        <f>D10/D32</f>
+        <f>D10/D28</f>
         <v/>
       </c>
     </row>
@@ -17414,7 +17414,7 @@
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>1576</v>
+        <v>1849</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>20</v>
@@ -17427,7 +17427,7 @@
         <v>2026</v>
       </c>
       <c r="F11" s="6">
-        <f>D11/D32</f>
+        <f>D11/D28</f>
         <v/>
       </c>
     </row>
@@ -17438,7 +17438,7 @@
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>537</v>
+        <v>675</v>
       </c>
       <c r="C12" s="4" t="n">
         <v>20</v>
@@ -17451,7 +17451,7 @@
         <v>2026</v>
       </c>
       <c r="F12" s="6">
-        <f>D12/D32</f>
+        <f>D12/D28</f>
         <v/>
       </c>
     </row>
@@ -17475,7 +17475,7 @@
         <v>2026</v>
       </c>
       <c r="F13" s="6">
-        <f>D13/D32</f>
+        <f>D13/D28</f>
         <v/>
       </c>
     </row>
@@ -17499,7 +17499,7 @@
         <v>2026</v>
       </c>
       <c r="F14" s="6">
-        <f>D14/D32</f>
+        <f>D14/D28</f>
         <v/>
       </c>
     </row>
@@ -17523,7 +17523,7 @@
         <v>2026</v>
       </c>
       <c r="F15" s="6">
-        <f>D15/D32</f>
+        <f>D15/D28</f>
         <v/>
       </c>
     </row>
@@ -17547,7 +17547,7 @@
         <v>2026</v>
       </c>
       <c r="F16" s="6">
-        <f>D16/D32</f>
+        <f>D16/D28</f>
         <v/>
       </c>
     </row>
@@ -17571,7 +17571,7 @@
         <v>2026</v>
       </c>
       <c r="F17" s="6">
-        <f>D17/D32</f>
+        <f>D17/D28</f>
         <v/>
       </c>
     </row>
@@ -17595,7 +17595,7 @@
         <v>2026</v>
       </c>
       <c r="F18" s="6">
-        <f>D18/D32</f>
+        <f>D18/D28</f>
         <v/>
       </c>
     </row>
@@ -17619,7 +17619,7 @@
         <v>2026</v>
       </c>
       <c r="F19" s="6">
-        <f>D19/D32</f>
+        <f>D19/D28</f>
         <v/>
       </c>
     </row>
@@ -17643,7 +17643,7 @@
         <v>2026</v>
       </c>
       <c r="F20" s="6">
-        <f>D20/D32</f>
+        <f>D20/D28</f>
         <v/>
       </c>
     </row>
@@ -17654,7 +17654,7 @@
         </is>
       </c>
       <c r="B21" s="6" t="n">
-        <v>643</v>
+        <v>4603</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>20</v>
@@ -17667,7 +17667,7 @@
         <v>2026</v>
       </c>
       <c r="F21" s="6">
-        <f>D21/D32</f>
+        <f>D21/D28</f>
         <v/>
       </c>
     </row>
@@ -17678,7 +17678,7 @@
         </is>
       </c>
       <c r="B22" s="6" t="n">
-        <v>4043</v>
+        <v>4305</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>20</v>
@@ -17691,7 +17691,7 @@
         <v>2026</v>
       </c>
       <c r="F22" s="6">
-        <f>D22/D32</f>
+        <f>D22/D28</f>
         <v/>
       </c>
     </row>
@@ -17715,7 +17715,7 @@
         <v>2026</v>
       </c>
       <c r="F23" s="6">
-        <f>D23/D32</f>
+        <f>D23/D28</f>
         <v/>
       </c>
     </row>
@@ -17738,7 +17738,7 @@
         <v>2026</v>
       </c>
       <c r="F24" s="6">
-        <f>D24/D32</f>
+        <f>D24/D28</f>
         <v/>
       </c>
     </row>
@@ -17761,7 +17761,7 @@
         <v>2026</v>
       </c>
       <c r="F25" s="6">
-        <f>D25/D32</f>
+        <f>D25/D28</f>
         <v/>
       </c>
     </row>
@@ -17785,7 +17785,7 @@
         <v>2026</v>
       </c>
       <c r="F26" s="6">
-        <f>D26/D32</f>
+        <f>D26/D28</f>
         <v/>
       </c>
     </row>
@@ -17809,123 +17809,27 @@
         <v>2026</v>
       </c>
       <c r="F27" s="6">
-        <f>D27/D32</f>
+        <f>D27/D28</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="6" t="inlineStr">
-        <is>
-          <t>LA ALBERCA</t>
-        </is>
-      </c>
-      <c r="B28" s="6" t="n">
-        <v>273</v>
-      </c>
-      <c r="C28" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="D28" s="4">
-        <f>B28*C28</f>
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>TOTAL MANO DE OBRA</t>
+        </is>
+      </c>
+      <c r="B28" s="7">
+        <f>SUM(B5:B27)</f>
         <v/>
       </c>
-      <c r="E28" s="6" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F28" s="6">
-        <f>D28/D32</f>
+      <c r="C28" s="8" t="n"/>
+      <c r="D28" s="8">
+        <f>SUM(D5:D27)</f>
         <v/>
       </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="6" t="inlineStr">
-        <is>
-          <t>BARINAS</t>
-        </is>
-      </c>
-      <c r="B29" s="6" t="n">
-        <v>138</v>
-      </c>
-      <c r="C29" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="D29" s="4">
-        <f>B29*C29</f>
-        <v/>
-      </c>
-      <c r="E29" s="6" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F29" s="6">
-        <f>D29/D32</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="6" t="inlineStr">
-        <is>
-          <t>FORMENTERA 14, JUANMA</t>
-        </is>
-      </c>
-      <c r="B30" s="6" t="n">
-        <v>3960</v>
-      </c>
-      <c r="C30" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="D30" s="4">
-        <f>B30*C30</f>
-        <v/>
-      </c>
-      <c r="E30" s="6" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F30" s="6">
-        <f>D30/D32</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="6" t="inlineStr">
-        <is>
-          <t>FORMENTERA 12, JOAQUIN</t>
-        </is>
-      </c>
-      <c r="B31" s="6" t="n">
-        <v>262</v>
-      </c>
-      <c r="C31" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="D31" s="4">
-        <f>B31*C31</f>
-        <v/>
-      </c>
-      <c r="E31" s="6" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F31" s="6">
-        <f>D31/D32</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="7" t="inlineStr">
-        <is>
-          <t>TOTAL MANO DE OBRA</t>
-        </is>
-      </c>
-      <c r="B32" s="7">
-        <f>SUM(B5:B31)</f>
-        <v/>
-      </c>
-      <c r="C32" s="8" t="n"/>
-      <c r="D32" s="8">
-        <f>SUM(D5:D31)</f>
-        <v/>
-      </c>
-      <c r="E32" s="7" t="n"/>
-      <c r="F32" s="7" t="n"/>
+      <c r="E28" s="7" t="n"/>
+      <c r="F28" s="7" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/ECO_STRUCT_Datos.xlsx
+++ b/ECO_STRUCT_Datos.xlsx
@@ -17558,7 +17558,7 @@
         </is>
       </c>
       <c r="B17" s="6" t="n">
-        <v>457</v>
+        <v>499</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>20</v>

--- a/ECO_STRUCT_Datos.xlsx
+++ b/ECO_STRUCT_Datos.xlsx
@@ -17558,7 +17558,7 @@
         </is>
       </c>
       <c r="B17" s="6" t="n">
-        <v>499</v>
+        <v>457</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>20</v>

--- a/ECO_STRUCT_Datos.xlsx
+++ b/ECO_STRUCT_Datos.xlsx
@@ -17434,7 +17434,7 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>26003 - BARINAS</t>
+          <t>260033 - BARINAS</t>
         </is>
       </c>
       <c r="B12" s="6" t="n">
@@ -17722,7 +17722,7 @@
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>MURO VECINO</t>
+          <t>2100 - MURO VECINO</t>
         </is>
       </c>
       <c r="B24" s="6" t="n">
@@ -17745,7 +17745,7 @@
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>OBRA CAMPO</t>
+          <t>2600 - OBRA CAMPO</t>
         </is>
       </c>
       <c r="B25" s="6" t="n">
@@ -17768,7 +17768,7 @@
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>ALBERTO Y EVA</t>
+          <t>26008 - ALBERTO Y EVA</t>
         </is>
       </c>
       <c r="B26" s="6" t="n">
@@ -17792,7 +17792,7 @@
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>OBRA C/HUERTO CAPUCHINOS, MURCIA</t>
+          <t>24008 - OBRA C/HUERTO CAPUCHINOS, MURCIA</t>
         </is>
       </c>
       <c r="B27" s="6" t="n">

--- a/ECO_STRUCT_Datos.xlsx
+++ b/ECO_STRUCT_Datos.xlsx
@@ -17986,7 +17986,7 @@
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>26007 OBRA HELENA Y JACOBO</t>
+          <t>26007 - OBRA HELENA Y JACOBO</t>
         </is>
       </c>
       <c r="B28" s="6" t="n">

--- a/ECO_STRUCT_Datos.xlsx
+++ b/ECO_STRUCT_Datos.xlsx
@@ -15590,7 +15590,7 @@
         </is>
       </c>
       <c r="B28" s="6" t="n">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="C28" s="4" t="n">
         <v>20</v>

--- a/ECO_STRUCT_Datos.xlsx
+++ b/ECO_STRUCT_Datos.xlsx
@@ -568,7 +568,7 @@
         </is>
       </c>
       <c r="B8" s="4">
-        <f>'Mano de Obra'!D29</f>
+        <f>'Mano de Obra'!D30</f>
         <v/>
       </c>
     </row>
@@ -14976,7 +14976,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -15053,7 +15053,7 @@
         <v>2026</v>
       </c>
       <c r="F5" s="6">
-        <f>D5/D29</f>
+        <f>D5/D30</f>
         <v/>
       </c>
     </row>
@@ -15077,7 +15077,7 @@
         <v>2026</v>
       </c>
       <c r="F6" s="6">
-        <f>D6/D29</f>
+        <f>D6/D30</f>
         <v/>
       </c>
     </row>
@@ -15101,7 +15101,7 @@
         <v>2026</v>
       </c>
       <c r="F7" s="6">
-        <f>D7/D29</f>
+        <f>D7/D30</f>
         <v/>
       </c>
     </row>
@@ -15125,7 +15125,7 @@
         <v>2026</v>
       </c>
       <c r="F8" s="6">
-        <f>D8/D29</f>
+        <f>D8/D30</f>
         <v/>
       </c>
     </row>
@@ -15149,7 +15149,7 @@
         <v>2026</v>
       </c>
       <c r="F9" s="6">
-        <f>D9/D29</f>
+        <f>D9/D30</f>
         <v/>
       </c>
     </row>
@@ -15173,7 +15173,7 @@
         <v>2026</v>
       </c>
       <c r="F10" s="6">
-        <f>D10/D29</f>
+        <f>D10/D30</f>
         <v/>
       </c>
     </row>
@@ -15197,7 +15197,7 @@
         <v>2026</v>
       </c>
       <c r="F11" s="6">
-        <f>D11/D29</f>
+        <f>D11/D30</f>
         <v/>
       </c>
     </row>
@@ -15221,7 +15221,7 @@
         <v>2026</v>
       </c>
       <c r="F12" s="6">
-        <f>D12/D29</f>
+        <f>D12/D30</f>
         <v/>
       </c>
     </row>
@@ -15232,7 +15232,7 @@
         </is>
       </c>
       <c r="B13" s="6" t="n">
-        <v>2192</v>
+        <v>2224</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>20</v>
@@ -15245,7 +15245,7 @@
         <v>2026</v>
       </c>
       <c r="F13" s="6">
-        <f>D13/D29</f>
+        <f>D13/D30</f>
         <v/>
       </c>
     </row>
@@ -15269,7 +15269,7 @@
         <v>2026</v>
       </c>
       <c r="F14" s="6">
-        <f>D14/D29</f>
+        <f>D14/D30</f>
         <v/>
       </c>
     </row>
@@ -15293,7 +15293,7 @@
         <v>2026</v>
       </c>
       <c r="F15" s="6">
-        <f>D15/D29</f>
+        <f>D15/D30</f>
         <v/>
       </c>
     </row>
@@ -15317,7 +15317,7 @@
         <v>2026</v>
       </c>
       <c r="F16" s="6">
-        <f>D16/D29</f>
+        <f>D16/D30</f>
         <v/>
       </c>
     </row>
@@ -15341,7 +15341,7 @@
         <v>2026</v>
       </c>
       <c r="F17" s="6">
-        <f>D17/D29</f>
+        <f>D17/D30</f>
         <v/>
       </c>
     </row>
@@ -15352,7 +15352,7 @@
         </is>
       </c>
       <c r="B18" s="6" t="n">
-        <v>971</v>
+        <v>995</v>
       </c>
       <c r="C18" s="4" t="n">
         <v>20</v>
@@ -15365,7 +15365,7 @@
         <v>2026</v>
       </c>
       <c r="F18" s="6">
-        <f>D18/D29</f>
+        <f>D18/D30</f>
         <v/>
       </c>
     </row>
@@ -15389,7 +15389,7 @@
         <v>2026</v>
       </c>
       <c r="F19" s="6">
-        <f>D19/D29</f>
+        <f>D19/D30</f>
         <v/>
       </c>
     </row>
@@ -15413,7 +15413,7 @@
         <v>2026</v>
       </c>
       <c r="F20" s="6">
-        <f>D20/D29</f>
+        <f>D20/D30</f>
         <v/>
       </c>
     </row>
@@ -15437,7 +15437,7 @@
         <v>2026</v>
       </c>
       <c r="F21" s="6">
-        <f>D21/D29</f>
+        <f>D21/D30</f>
         <v/>
       </c>
     </row>
@@ -15461,7 +15461,7 @@
         <v>2026</v>
       </c>
       <c r="F22" s="6">
-        <f>D22/D29</f>
+        <f>D22/D30</f>
         <v/>
       </c>
     </row>
@@ -15485,7 +15485,7 @@
         <v>2026</v>
       </c>
       <c r="F23" s="6">
-        <f>D23/D29</f>
+        <f>D23/D30</f>
         <v/>
       </c>
     </row>
@@ -15508,7 +15508,7 @@
         <v>2026</v>
       </c>
       <c r="F24" s="6">
-        <f>D24/D29</f>
+        <f>D24/D30</f>
         <v/>
       </c>
     </row>
@@ -15531,7 +15531,7 @@
         <v>2026</v>
       </c>
       <c r="F25" s="6">
-        <f>D25/D29</f>
+        <f>D25/D30</f>
         <v/>
       </c>
     </row>
@@ -15542,7 +15542,7 @@
         </is>
       </c>
       <c r="B26" s="6" t="n">
-        <v>289</v>
+        <v>321</v>
       </c>
       <c r="C26" s="4" t="n">
         <v>20</v>
@@ -15555,7 +15555,7 @@
         <v>2026</v>
       </c>
       <c r="F26" s="6">
-        <f>D26/D29</f>
+        <f>D26/D30</f>
         <v/>
       </c>
     </row>
@@ -15579,7 +15579,7 @@
         <v>2026</v>
       </c>
       <c r="F27" s="6">
-        <f>D27/D29</f>
+        <f>D27/D30</f>
         <v/>
       </c>
     </row>
@@ -15603,27 +15603,51 @@
         <v>2026</v>
       </c>
       <c r="F28" s="6">
-        <f>D28/D29</f>
+        <f>D28/D30</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="7" t="inlineStr">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>26021 - OBRA CRISTINA RESTAURANTE, ALICANTE</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="C29" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="D29" s="4">
+        <f>B29*C29</f>
+        <v/>
+      </c>
+      <c r="E29" s="6" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F29" s="6">
+        <f>D29/D30</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="inlineStr">
         <is>
           <t>TOTAL MANO DE OBRA</t>
         </is>
       </c>
-      <c r="B29" s="7">
-        <f>SUM(B5:B28)</f>
+      <c r="B30" s="7">
+        <f>SUM(B5:B29)</f>
         <v/>
       </c>
-      <c r="C29" s="8" t="n"/>
-      <c r="D29" s="8">
-        <f>SUM(D5:D28)</f>
+      <c r="C30" s="8" t="n"/>
+      <c r="D30" s="8">
+        <f>SUM(D5:D29)</f>
         <v/>
       </c>
-      <c r="E29" s="7" t="n"/>
-      <c r="F29" s="7" t="n"/>
+      <c r="E30" s="7" t="n"/>
+      <c r="F30" s="7" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/ECO_STRUCT_Datos.xlsx
+++ b/ECO_STRUCT_Datos.xlsx
@@ -1490,7 +1490,7 @@
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>24017 - GARAJE MURCIA</t>
+          <t>26002 - GARAJE MURCIA</t>
         </is>
       </c>
       <c r="C4" s="4" t="n">
@@ -2990,7 +2990,7 @@
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>24017 - GARAJE MURCIA</t>
+          <t>26002 - GARAJE MURCIA</t>
         </is>
       </c>
       <c r="B25" s="4" t="n">
@@ -47887,23 +47887,23 @@
     <row r="1511">
       <c r="A1511" s="6" t="inlineStr">
         <is>
-          <t>24017 - GARAJE MURCIA</t>
+          <t>24018 - OBRA LUC2</t>
         </is>
       </c>
       <c r="B1511" s="6" t="inlineStr">
         <is>
-          <t>1.173,00</t>
+          <t>1.100,00</t>
         </is>
       </c>
       <c r="C1511" s="6" t="inlineStr"/>
       <c r="D1511" s="6" t="inlineStr">
         <is>
-          <t>INTALACIÓN COMPLETA DE ELECTRICIDAD EN GARAJE</t>
+          <t>HIERRO CIMENTACIÓN Y FORJADO</t>
         </is>
       </c>
       <c r="E1511" s="6" t="inlineStr">
         <is>
-          <t>MOVE2GO SL.</t>
+          <t>FERRALLAS MONFORTE DEL CID SL.</t>
         </is>
       </c>
       <c r="F1511" s="6" t="inlineStr">
@@ -47912,29 +47912,29 @@
         </is>
       </c>
       <c r="G1511" s="4" t="n">
-        <v>1087.5</v>
+        <v>4086.16</v>
       </c>
     </row>
     <row r="1512">
       <c r="A1512" s="6" t="inlineStr">
         <is>
-          <t>24017 - GARAJE MURCIA</t>
+          <t>24018 - OBRA LUC2</t>
         </is>
       </c>
       <c r="B1512" s="6" t="inlineStr">
         <is>
-          <t>851,00</t>
+          <t>862,00</t>
         </is>
       </c>
       <c r="C1512" s="6" t="inlineStr"/>
       <c r="D1512" s="6" t="inlineStr">
         <is>
-          <t>INTALACIÓN COMPLETA DE ELECTRICIDAD EN GARAJE</t>
+          <t>EXCAVACIÓN CIMENTACIÓN</t>
         </is>
       </c>
       <c r="E1512" s="6" t="inlineStr">
         <is>
-          <t>MOVE2GO SL.</t>
+          <t>TREXGRUCO SL.</t>
         </is>
       </c>
       <c r="F1512" s="6" t="inlineStr">
@@ -47943,24 +47943,24 @@
         </is>
       </c>
       <c r="G1512" s="4" t="n">
-        <v>1087.5</v>
+        <v>3947.76</v>
       </c>
     </row>
     <row r="1513">
       <c r="A1513" s="6" t="inlineStr">
         <is>
-          <t>24017 - GARAJE MURCIA</t>
+          <t>24018 - OBRA LUC2</t>
         </is>
       </c>
       <c r="B1513" s="6" t="inlineStr">
         <is>
-          <t>874,00</t>
+          <t>1.242,00</t>
         </is>
       </c>
       <c r="C1513" s="6" t="inlineStr"/>
       <c r="D1513" s="6" t="inlineStr">
         <is>
-          <t>LEROY MERLIN (PRESUPUESTO 603119) FOTO EN DOCUMENTOS</t>
+          <t>Presupuesto nº 614823</t>
         </is>
       </c>
       <c r="E1513" s="6" t="inlineStr">
@@ -47974,24 +47974,24 @@
         </is>
       </c>
       <c r="G1513" s="4" t="n">
-        <v>469.96</v>
+        <v>2780.18</v>
       </c>
     </row>
     <row r="1514">
       <c r="A1514" s="6" t="inlineStr">
         <is>
-          <t>24017 - GARAJE MURCIA</t>
+          <t>24018 - OBRA LUC2</t>
         </is>
       </c>
       <c r="B1514" s="6" t="inlineStr">
         <is>
-          <t>853,00</t>
+          <t>1.113,00</t>
         </is>
       </c>
       <c r="C1514" s="6" t="inlineStr"/>
       <c r="D1514" s="6" t="inlineStr">
         <is>
-          <t>LEROY MERLIN (PRESUPUESTO 602161) FOTO EN DOCUMENTOS</t>
+          <t>MATERIAL OBRA</t>
         </is>
       </c>
       <c r="E1514" s="6" t="inlineStr">
@@ -48005,24 +48005,24 @@
         </is>
       </c>
       <c r="G1514" s="4" t="n">
-        <v>352.76</v>
+        <v>2693.07</v>
       </c>
     </row>
     <row r="1515">
       <c r="A1515" s="6" t="inlineStr">
         <is>
-          <t>24017 - GARAJE MURCIA</t>
+          <t>24018 - OBRA LUC2</t>
         </is>
       </c>
       <c r="B1515" s="6" t="inlineStr">
         <is>
-          <t>852,00</t>
+          <t>1.151,00</t>
         </is>
       </c>
       <c r="C1515" s="6" t="inlineStr"/>
       <c r="D1515" s="6" t="inlineStr">
         <is>
-          <t>LEROY MERLIN (DUPLICADO PRESUPUESTO 601689) FOTO EN DOCUMENTOS</t>
+          <t>MATERIAL OBRA</t>
         </is>
       </c>
       <c r="E1515" s="6" t="inlineStr">
@@ -48036,7 +48036,7 @@
         </is>
       </c>
       <c r="G1515" s="4" t="n">
-        <v>352.76</v>
+        <v>2656.74</v>
       </c>
     </row>
     <row r="1516">
@@ -48047,18 +48047,18 @@
       </c>
       <c r="B1516" s="6" t="inlineStr">
         <is>
-          <t>1.100,00</t>
+          <t>1.545,00</t>
         </is>
       </c>
       <c r="C1516" s="6" t="inlineStr"/>
       <c r="D1516" s="6" t="inlineStr">
         <is>
-          <t>HIERRO CIMENTACIÓN Y FORJADO</t>
+          <t>HORMIGON</t>
         </is>
       </c>
       <c r="E1516" s="6" t="inlineStr">
         <is>
-          <t>FERRALLAS MONFORTE DEL CID SL.</t>
+          <t>CANTERAS Y RECICLADOS SL.</t>
         </is>
       </c>
       <c r="F1516" s="6" t="inlineStr">
@@ -48067,7 +48067,7 @@
         </is>
       </c>
       <c r="G1516" s="4" t="n">
-        <v>4086.16</v>
+        <v>2595</v>
       </c>
     </row>
     <row r="1517">
@@ -48078,18 +48078,18 @@
       </c>
       <c r="B1517" s="6" t="inlineStr">
         <is>
-          <t>862,00</t>
+          <t>1.278,00</t>
         </is>
       </c>
       <c r="C1517" s="6" t="inlineStr"/>
       <c r="D1517" s="6" t="inlineStr">
         <is>
-          <t>EXCAVACIÓN CIMENTACIÓN</t>
+          <t>PRESUPUESTO 616670</t>
         </is>
       </c>
       <c r="E1517" s="6" t="inlineStr">
         <is>
-          <t>TREXGRUCO SL.</t>
+          <t>LEROY MERLIN ESPAÑA SL</t>
         </is>
       </c>
       <c r="F1517" s="6" t="inlineStr">
@@ -48098,7 +48098,7 @@
         </is>
       </c>
       <c r="G1517" s="4" t="n">
-        <v>3947.76</v>
+        <v>2499.9</v>
       </c>
     </row>
     <row r="1518">
@@ -48109,18 +48109,18 @@
       </c>
       <c r="B1518" s="6" t="inlineStr">
         <is>
-          <t>1.242,00</t>
+          <t>1.202,00</t>
         </is>
       </c>
       <c r="C1518" s="6" t="inlineStr"/>
       <c r="D1518" s="6" t="inlineStr">
         <is>
-          <t>Presupuesto nº 614823</t>
+          <t>HORMIGON LLENADO MUROS</t>
         </is>
       </c>
       <c r="E1518" s="6" t="inlineStr">
         <is>
-          <t>LEROY MERLIN ESPAÑA SL</t>
+          <t>ARIDOS Y HORMIGONES CUTILLAS S.L.</t>
         </is>
       </c>
       <c r="F1518" s="6" t="inlineStr">
@@ -48129,7 +48129,7 @@
         </is>
       </c>
       <c r="G1518" s="4" t="n">
-        <v>2780.18</v>
+        <v>2256</v>
       </c>
     </row>
     <row r="1519">
@@ -48140,18 +48140,18 @@
       </c>
       <c r="B1519" s="6" t="inlineStr">
         <is>
-          <t>1.113,00</t>
+          <t>1.129,00</t>
         </is>
       </c>
       <c r="C1519" s="6" t="inlineStr"/>
       <c r="D1519" s="6" t="inlineStr">
         <is>
-          <t>MATERIAL OBRA</t>
+          <t>HORMIGÓN CIMENTACIÓN</t>
         </is>
       </c>
       <c r="E1519" s="6" t="inlineStr">
         <is>
-          <t>LEROY MERLIN ESPAÑA SL</t>
+          <t>ARIDOS Y HORMIGONES CUTILLAS S.L.</t>
         </is>
       </c>
       <c r="F1519" s="6" t="inlineStr">
@@ -48160,7 +48160,7 @@
         </is>
       </c>
       <c r="G1519" s="4" t="n">
-        <v>2693.07</v>
+        <v>1710</v>
       </c>
     </row>
     <row r="1520">
@@ -48171,18 +48171,18 @@
       </c>
       <c r="B1520" s="6" t="inlineStr">
         <is>
-          <t>1.151,00</t>
+          <t>891,00</t>
         </is>
       </c>
       <c r="C1520" s="6" t="inlineStr"/>
       <c r="D1520" s="6" t="inlineStr">
         <is>
-          <t>MATERIAL OBRA</t>
+          <t>EXCAVACIÓN CIMENTACION</t>
         </is>
       </c>
       <c r="E1520" s="6" t="inlineStr">
         <is>
-          <t>LEROY MERLIN ESPAÑA SL</t>
+          <t>TREXGRUCO SL.</t>
         </is>
       </c>
       <c r="F1520" s="6" t="inlineStr">
@@ -48191,7 +48191,7 @@
         </is>
       </c>
       <c r="G1520" s="4" t="n">
-        <v>2656.74</v>
+        <v>1624</v>
       </c>
     </row>
     <row r="1521">
@@ -48202,18 +48202,18 @@
       </c>
       <c r="B1521" s="6" t="inlineStr">
         <is>
-          <t>1.545,00</t>
+          <t>1.256,00</t>
         </is>
       </c>
       <c r="C1521" s="6" t="inlineStr"/>
       <c r="D1521" s="6" t="inlineStr">
         <is>
-          <t>HORMIGON</t>
+          <t>LLENADO FORJADO #llenado forjado sotano</t>
         </is>
       </c>
       <c r="E1521" s="6" t="inlineStr">
         <is>
-          <t>CANTERAS Y RECICLADOS SL.</t>
+          <t>ARIDOS Y HORMIGONES CUTILLAS S.L.</t>
         </is>
       </c>
       <c r="F1521" s="6" t="inlineStr">
@@ -48222,7 +48222,7 @@
         </is>
       </c>
       <c r="G1521" s="4" t="n">
-        <v>2595</v>
+        <v>1620</v>
       </c>
     </row>
     <row r="1522">
@@ -48233,18 +48233,18 @@
       </c>
       <c r="B1522" s="6" t="inlineStr">
         <is>
-          <t>1.278,00</t>
+          <t>1.525,00</t>
         </is>
       </c>
       <c r="C1522" s="6" t="inlineStr"/>
       <c r="D1522" s="6" t="inlineStr">
         <is>
-          <t>PRESUPUESTO 616670</t>
+          <t>GRUA</t>
         </is>
       </c>
       <c r="E1522" s="6" t="inlineStr">
         <is>
-          <t>LEROY MERLIN ESPAÑA SL</t>
+          <t>GRUAS Y MAQUINARIA PETREL SL</t>
         </is>
       </c>
       <c r="F1522" s="6" t="inlineStr">
@@ -48253,7 +48253,7 @@
         </is>
       </c>
       <c r="G1522" s="4" t="n">
-        <v>2499.9</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="1523">
@@ -48264,18 +48264,18 @@
       </c>
       <c r="B1523" s="6" t="inlineStr">
         <is>
-          <t>1.202,00</t>
+          <t>1.164,00</t>
         </is>
       </c>
       <c r="C1523" s="6" t="inlineStr"/>
       <c r="D1523" s="6" t="inlineStr">
         <is>
-          <t>HORMIGON LLENADO MUROS</t>
+          <t>GRUA #montar ferralla y repartir</t>
         </is>
       </c>
       <c r="E1523" s="6" t="inlineStr">
         <is>
-          <t>ARIDOS Y HORMIGONES CUTILLAS S.L.</t>
+          <t>GRUAS Y MAQUINARIA PETREL SL</t>
         </is>
       </c>
       <c r="F1523" s="6" t="inlineStr">
@@ -48284,7 +48284,7 @@
         </is>
       </c>
       <c r="G1523" s="4" t="n">
-        <v>2256</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="1524">
@@ -48295,18 +48295,18 @@
       </c>
       <c r="B1524" s="6" t="inlineStr">
         <is>
-          <t>1.129,00</t>
+          <t>1.102,00</t>
         </is>
       </c>
       <c r="C1524" s="6" t="inlineStr"/>
       <c r="D1524" s="6" t="inlineStr">
         <is>
-          <t>HORMIGÓN CIMENTACIÓN</t>
+          <t>ALQUILER DUMPER CIMENTACION</t>
         </is>
       </c>
       <c r="E1524" s="6" t="inlineStr">
         <is>
-          <t>ARIDOS Y HORMIGONES CUTILLAS S.L.</t>
+          <t>CHOOSEMAK SOCIEDAD DE RESPONSABILIDAD LIMITADA</t>
         </is>
       </c>
       <c r="F1524" s="6" t="inlineStr">
@@ -48315,7 +48315,7 @@
         </is>
       </c>
       <c r="G1524" s="4" t="n">
-        <v>1710</v>
+        <v>1254.74</v>
       </c>
     </row>
     <row r="1525">
@@ -48326,18 +48326,18 @@
       </c>
       <c r="B1525" s="6" t="inlineStr">
         <is>
-          <t>891,00</t>
+          <t>1.272,00</t>
         </is>
       </c>
       <c r="C1525" s="6" t="inlineStr"/>
       <c r="D1525" s="6" t="inlineStr">
         <is>
-          <t>EXCAVACIÓN CIMENTACION</t>
+          <t>GRUA #grua</t>
         </is>
       </c>
       <c r="E1525" s="6" t="inlineStr">
         <is>
-          <t>TREXGRUCO SL.</t>
+          <t>GRUAS Y TRANSPORTES ESPECIALES EL ALICANTI SL.</t>
         </is>
       </c>
       <c r="F1525" s="6" t="inlineStr">
@@ -48346,7 +48346,7 @@
         </is>
       </c>
       <c r="G1525" s="4" t="n">
-        <v>1624</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="1526">
@@ -48357,18 +48357,18 @@
       </c>
       <c r="B1526" s="6" t="inlineStr">
         <is>
-          <t>1.256,00</t>
+          <t>1.664,00</t>
         </is>
       </c>
       <c r="C1526" s="6" t="inlineStr"/>
       <c r="D1526" s="6" t="inlineStr">
         <is>
-          <t>LLENADO FORJADO #llenado forjado sotano</t>
+          <t>BOMBA LORENZO</t>
         </is>
       </c>
       <c r="E1526" s="6" t="inlineStr">
         <is>
-          <t>ARIDOS Y HORMIGONES CUTILLAS S.L.</t>
+          <t>LORENZO ROMERO MORALEDA</t>
         </is>
       </c>
       <c r="F1526" s="6" t="inlineStr">
@@ -48377,7 +48377,7 @@
         </is>
       </c>
       <c r="G1526" s="4" t="n">
-        <v>1620</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="1527">
@@ -48388,18 +48388,18 @@
       </c>
       <c r="B1527" s="6" t="inlineStr">
         <is>
-          <t>1.525,00</t>
+          <t>1.769,00</t>
         </is>
       </c>
       <c r="C1527" s="6" t="inlineStr"/>
       <c r="D1527" s="6" t="inlineStr">
         <is>
-          <t>GRUA</t>
+          <t>BOMBA HORMIGON</t>
         </is>
       </c>
       <c r="E1527" s="6" t="inlineStr">
         <is>
-          <t>GRUAS Y MAQUINARIA PETREL SL</t>
+          <t>LORENZO ROMERO MORALEDA</t>
         </is>
       </c>
       <c r="F1527" s="6" t="inlineStr">
@@ -48408,7 +48408,7 @@
         </is>
       </c>
       <c r="G1527" s="4" t="n">
-        <v>1560</v>
+        <v>950</v>
       </c>
     </row>
     <row r="1528">
@@ -48419,18 +48419,18 @@
       </c>
       <c r="B1528" s="6" t="inlineStr">
         <is>
-          <t>1.164,00</t>
+          <t>1.492,00</t>
         </is>
       </c>
       <c r="C1528" s="6" t="inlineStr"/>
       <c r="D1528" s="6" t="inlineStr">
         <is>
-          <t>GRUA #montar ferralla y repartir</t>
+          <t>PRESUPUESTO Nº 613788</t>
         </is>
       </c>
       <c r="E1528" s="6" t="inlineStr">
         <is>
-          <t>GRUAS Y MAQUINARIA PETREL SL</t>
+          <t>LEROY MERLIN ESPAÑA SL</t>
         </is>
       </c>
       <c r="F1528" s="6" t="inlineStr">
@@ -48439,7 +48439,7 @@
         </is>
       </c>
       <c r="G1528" s="4" t="n">
-        <v>1470</v>
+        <v>911.61</v>
       </c>
     </row>
     <row r="1529">
@@ -48450,18 +48450,18 @@
       </c>
       <c r="B1529" s="6" t="inlineStr">
         <is>
-          <t>1.102,00</t>
+          <t>854,00</t>
         </is>
       </c>
       <c r="C1529" s="6" t="inlineStr"/>
       <c r="D1529" s="6" t="inlineStr">
         <is>
-          <t>ALQUILER DUMPER CIMENTACION</t>
+          <t>VIAJES ESCOMBRO PINOSO-BARINAS</t>
         </is>
       </c>
       <c r="E1529" s="6" t="inlineStr">
         <is>
-          <t>CHOOSEMAK SOCIEDAD DE RESPONSABILIDAD LIMITADA</t>
+          <t>TRASERCO COOP VALENCIANA</t>
         </is>
       </c>
       <c r="F1529" s="6" t="inlineStr">
@@ -48470,7 +48470,7 @@
         </is>
       </c>
       <c r="G1529" s="4" t="n">
-        <v>1254.74</v>
+        <v>900</v>
       </c>
     </row>
     <row r="1530">
@@ -48481,18 +48481,18 @@
       </c>
       <c r="B1530" s="6" t="inlineStr">
         <is>
-          <t>1.272,00</t>
+          <t>1.539,00</t>
         </is>
       </c>
       <c r="C1530" s="6" t="inlineStr"/>
       <c r="D1530" s="6" t="inlineStr">
         <is>
-          <t>GRUA #grua</t>
+          <t>MATERIAL Y FONTANERIA</t>
         </is>
       </c>
       <c r="E1530" s="6" t="inlineStr">
         <is>
-          <t>GRUAS Y TRANSPORTES ESPECIALES EL ALICANTI SL.</t>
+          <t>MATERIALES DE CONSTRUCCION LOS CAPITOS SL.</t>
         </is>
       </c>
       <c r="F1530" s="6" t="inlineStr">
@@ -48501,7 +48501,7 @@
         </is>
       </c>
       <c r="G1530" s="4" t="n">
-        <v>1170</v>
+        <v>827.84</v>
       </c>
     </row>
     <row r="1531">
@@ -48512,13 +48512,13 @@
       </c>
       <c r="B1531" s="6" t="inlineStr">
         <is>
-          <t>1.664,00</t>
+          <t>1.661,00</t>
         </is>
       </c>
       <c r="C1531" s="6" t="inlineStr"/>
       <c r="D1531" s="6" t="inlineStr">
         <is>
-          <t>BOMBA LORENZO</t>
+          <t>BOMBA LORNZO</t>
         </is>
       </c>
       <c r="E1531" s="6" t="inlineStr">
@@ -48532,7 +48532,7 @@
         </is>
       </c>
       <c r="G1531" s="4" t="n">
-        <v>1000</v>
+        <v>790</v>
       </c>
     </row>
     <row r="1532">
@@ -48543,18 +48543,18 @@
       </c>
       <c r="B1532" s="6" t="inlineStr">
         <is>
-          <t>1.769,00</t>
+          <t>1.477,00</t>
         </is>
       </c>
       <c r="C1532" s="6" t="inlineStr"/>
       <c r="D1532" s="6" t="inlineStr">
         <is>
-          <t>BOMBA HORMIGON</t>
+          <t>KG ACERO FERRALLADO</t>
         </is>
       </c>
       <c r="E1532" s="6" t="inlineStr">
         <is>
-          <t>LORENZO ROMERO MORALEDA</t>
+          <t>FERRALLAS MONFORTE DEL CID SL.</t>
         </is>
       </c>
       <c r="F1532" s="6" t="inlineStr">
@@ -48563,7 +48563,7 @@
         </is>
       </c>
       <c r="G1532" s="4" t="n">
-        <v>950</v>
+        <v>788.5</v>
       </c>
     </row>
     <row r="1533">
@@ -48574,18 +48574,18 @@
       </c>
       <c r="B1533" s="6" t="inlineStr">
         <is>
-          <t>1.492,00</t>
+          <t>1.253,00</t>
         </is>
       </c>
       <c r="C1533" s="6" t="inlineStr"/>
       <c r="D1533" s="6" t="inlineStr">
         <is>
-          <t>PRESUPUESTO Nº 613788</t>
+          <t>GRUA</t>
         </is>
       </c>
       <c r="E1533" s="6" t="inlineStr">
         <is>
-          <t>LEROY MERLIN ESPAÑA SL</t>
+          <t>GRUAS Y MAQUINARIA PETREL SL</t>
         </is>
       </c>
       <c r="F1533" s="6" t="inlineStr">
@@ -48594,7 +48594,7 @@
         </is>
       </c>
       <c r="G1533" s="4" t="n">
-        <v>911.61</v>
+        <v>720</v>
       </c>
     </row>
     <row r="1534">
@@ -48605,18 +48605,18 @@
       </c>
       <c r="B1534" s="6" t="inlineStr">
         <is>
-          <t>854,00</t>
+          <t>1.478,00</t>
         </is>
       </c>
       <c r="C1534" s="6" t="inlineStr"/>
       <c r="D1534" s="6" t="inlineStr">
         <is>
-          <t>VIAJES ESCOMBRO PINOSO-BARINAS</t>
+          <t>GRUA</t>
         </is>
       </c>
       <c r="E1534" s="6" t="inlineStr">
         <is>
-          <t>TRASERCO COOP VALENCIANA</t>
+          <t>GRUAS Y MAQUINARIA PETREL SL</t>
         </is>
       </c>
       <c r="F1534" s="6" t="inlineStr">
@@ -48625,7 +48625,7 @@
         </is>
       </c>
       <c r="G1534" s="4" t="n">
-        <v>900</v>
+        <v>715</v>
       </c>
     </row>
     <row r="1535">
@@ -48636,18 +48636,18 @@
       </c>
       <c r="B1535" s="6" t="inlineStr">
         <is>
-          <t>1.539,00</t>
+          <t>1.141,00</t>
         </is>
       </c>
       <c r="C1535" s="6" t="inlineStr"/>
       <c r="D1535" s="6" t="inlineStr">
         <is>
-          <t>MATERIAL Y FONTANERIA</t>
+          <t>BOMBA CIMENTACION</t>
         </is>
       </c>
       <c r="E1535" s="6" t="inlineStr">
         <is>
-          <t>MATERIALES DE CONSTRUCCION LOS CAPITOS SL.</t>
+          <t>LORENZO ROMERO MORALEDA</t>
         </is>
       </c>
       <c r="F1535" s="6" t="inlineStr">
@@ -48656,7 +48656,7 @@
         </is>
       </c>
       <c r="G1535" s="4" t="n">
-        <v>827.84</v>
+        <v>700</v>
       </c>
     </row>
     <row r="1536">
@@ -48667,18 +48667,18 @@
       </c>
       <c r="B1536" s="6" t="inlineStr">
         <is>
-          <t>1.661,00</t>
+          <t>1.207,00</t>
         </is>
       </c>
       <c r="C1536" s="6" t="inlineStr"/>
       <c r="D1536" s="6" t="inlineStr">
         <is>
-          <t>BOMBA LORNZO</t>
+          <t>SACA GRAVA + PORTE</t>
         </is>
       </c>
       <c r="E1536" s="6" t="inlineStr">
         <is>
-          <t>LORENZO ROMERO MORALEDA</t>
+          <t>MATERIALES DE CONSTRUCCION LOS CAPITOS SL.</t>
         </is>
       </c>
       <c r="F1536" s="6" t="inlineStr">
@@ -48687,7 +48687,7 @@
         </is>
       </c>
       <c r="G1536" s="4" t="n">
-        <v>790</v>
+        <v>600.9</v>
       </c>
     </row>
     <row r="1537">
@@ -48698,18 +48698,18 @@
       </c>
       <c r="B1537" s="6" t="inlineStr">
         <is>
-          <t>1.477,00</t>
+          <t>1.177,00</t>
         </is>
       </c>
       <c r="C1537" s="6" t="inlineStr"/>
       <c r="D1537" s="6" t="inlineStr">
         <is>
-          <t>KG ACERO FERRALLADO</t>
+          <t>PRESUPUESTO Nº 611490</t>
         </is>
       </c>
       <c r="E1537" s="6" t="inlineStr">
         <is>
-          <t>FERRALLAS MONFORTE DEL CID SL.</t>
+          <t>LEROY MERLIN ESPAÑA SL</t>
         </is>
       </c>
       <c r="F1537" s="6" t="inlineStr">
@@ -48718,7 +48718,7 @@
         </is>
       </c>
       <c r="G1537" s="4" t="n">
-        <v>788.5</v>
+        <v>528.26</v>
       </c>
     </row>
     <row r="1538">
@@ -48729,27 +48729,23 @@
       </c>
       <c r="B1538" s="6" t="inlineStr">
         <is>
-          <t>1.253,00</t>
+          <t>1.149,00</t>
         </is>
       </c>
       <c r="C1538" s="6" t="inlineStr"/>
       <c r="D1538" s="6" t="inlineStr">
         <is>
-          <t>GRUA</t>
-        </is>
-      </c>
-      <c r="E1538" s="6" t="inlineStr">
-        <is>
-          <t>GRUAS Y MAQUINARIA PETREL SL</t>
-        </is>
-      </c>
+          <t>Tasas declaracion responsable</t>
+        </is>
+      </c>
+      <c r="E1538" s="6" t="inlineStr"/>
       <c r="F1538" s="6" t="inlineStr">
         <is>
           <t>IMPUTADO</t>
         </is>
       </c>
       <c r="G1538" s="4" t="n">
-        <v>720</v>
+        <v>429</v>
       </c>
     </row>
     <row r="1539">
@@ -48760,18 +48756,18 @@
       </c>
       <c r="B1539" s="6" t="inlineStr">
         <is>
-          <t>1.478,00</t>
+          <t>1.097,00</t>
         </is>
       </c>
       <c r="C1539" s="6" t="inlineStr"/>
       <c r="D1539" s="6" t="inlineStr">
         <is>
-          <t>GRUA</t>
+          <t>PRESUPUESTO Nº 610328</t>
         </is>
       </c>
       <c r="E1539" s="6" t="inlineStr">
         <is>
-          <t>GRUAS Y MAQUINARIA PETREL SL</t>
+          <t>LEROY MERLIN ESPAÑA SL</t>
         </is>
       </c>
       <c r="F1539" s="6" t="inlineStr">
@@ -48780,7 +48776,7 @@
         </is>
       </c>
       <c r="G1539" s="4" t="n">
-        <v>715</v>
+        <v>268.76</v>
       </c>
     </row>
     <row r="1540">
@@ -48791,18 +48787,18 @@
       </c>
       <c r="B1540" s="6" t="inlineStr">
         <is>
-          <t>1.141,00</t>
+          <t>788,00</t>
         </is>
       </c>
       <c r="C1540" s="6" t="inlineStr"/>
       <c r="D1540" s="6" t="inlineStr">
         <is>
-          <t>BOMBA CIMENTACION</t>
+          <t>VERTEDERO TIERRAS</t>
         </is>
       </c>
       <c r="E1540" s="6" t="inlineStr">
         <is>
-          <t>LORENZO ROMERO MORALEDA</t>
+          <t>ARIDOS Y PREFABRICADOS BARINAS SL</t>
         </is>
       </c>
       <c r="F1540" s="6" t="inlineStr">
@@ -48811,7 +48807,7 @@
         </is>
       </c>
       <c r="G1540" s="4" t="n">
-        <v>700</v>
+        <v>199.57</v>
       </c>
     </row>
     <row r="1541">
@@ -48822,13 +48818,13 @@
       </c>
       <c r="B1541" s="6" t="inlineStr">
         <is>
-          <t>1.207,00</t>
+          <t>1.480,00</t>
         </is>
       </c>
       <c r="C1541" s="6" t="inlineStr"/>
       <c r="D1541" s="6" t="inlineStr">
         <is>
-          <t>SACA GRAVA + PORTE</t>
+          <t>SACA ARENA</t>
         </is>
       </c>
       <c r="E1541" s="6" t="inlineStr">
@@ -48842,7 +48838,7 @@
         </is>
       </c>
       <c r="G1541" s="4" t="n">
-        <v>600.9</v>
+        <v>192.4</v>
       </c>
     </row>
     <row r="1542">
@@ -48853,13 +48849,13 @@
       </c>
       <c r="B1542" s="6" t="inlineStr">
         <is>
-          <t>1.177,00</t>
+          <t>1.276,00</t>
         </is>
       </c>
       <c r="C1542" s="6" t="inlineStr"/>
       <c r="D1542" s="6" t="inlineStr">
         <is>
-          <t>PRESUPUESTO Nº 611490</t>
+          <t>PRESUPUESTO 616437</t>
         </is>
       </c>
       <c r="E1542" s="6" t="inlineStr">
@@ -48873,7 +48869,7 @@
         </is>
       </c>
       <c r="G1542" s="4" t="n">
-        <v>528.26</v>
+        <v>183.24</v>
       </c>
     </row>
     <row r="1543">
@@ -48884,23 +48880,27 @@
       </c>
       <c r="B1543" s="6" t="inlineStr">
         <is>
-          <t>1.149,00</t>
+          <t>789,00</t>
         </is>
       </c>
       <c r="C1543" s="6" t="inlineStr"/>
       <c r="D1543" s="6" t="inlineStr">
         <is>
-          <t>Tasas declaracion responsable</t>
-        </is>
-      </c>
-      <c r="E1543" s="6" t="inlineStr"/>
+          <t>DESBROCE SOLAR</t>
+        </is>
+      </c>
+      <c r="E1543" s="6" t="inlineStr">
+        <is>
+          <t>MARCOS GALIANO POVEDA</t>
+        </is>
+      </c>
       <c r="F1543" s="6" t="inlineStr">
         <is>
           <t>IMPUTADO</t>
         </is>
       </c>
       <c r="G1543" s="4" t="n">
-        <v>429</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1544">
@@ -48911,18 +48911,18 @@
       </c>
       <c r="B1544" s="6" t="inlineStr">
         <is>
-          <t>1.097,00</t>
+          <t>595,00</t>
         </is>
       </c>
       <c r="C1544" s="6" t="inlineStr"/>
       <c r="D1544" s="6" t="inlineStr">
         <is>
-          <t>PRESUPUESTO Nº 610328</t>
+          <t>VALLA MOVIL TIPO S</t>
         </is>
       </c>
       <c r="E1544" s="6" t="inlineStr">
         <is>
-          <t>LEROY MERLIN ESPAÑA SL</t>
+          <t>MATERIALES DE CONSTRUCCION LOS CAPITOS SL.</t>
         </is>
       </c>
       <c r="F1544" s="6" t="inlineStr">
@@ -48931,7 +48931,7 @@
         </is>
       </c>
       <c r="G1544" s="4" t="n">
-        <v>268.76</v>
+        <v>132.98</v>
       </c>
     </row>
     <row r="1545">
@@ -48942,18 +48942,18 @@
       </c>
       <c r="B1545" s="6" t="inlineStr">
         <is>
-          <t>788,00</t>
+          <t>1.103,00</t>
         </is>
       </c>
       <c r="C1545" s="6" t="inlineStr"/>
       <c r="D1545" s="6" t="inlineStr">
         <is>
-          <t>VERTEDERO TIERRAS</t>
+          <t>DUMPER PINCHAZO</t>
         </is>
       </c>
       <c r="E1545" s="6" t="inlineStr">
         <is>
-          <t>ARIDOS Y PREFABRICADOS BARINAS SL</t>
+          <t>CHOOSEMAK SOCIEDAD DE RESPONSABILIDAD LIMITADA</t>
         </is>
       </c>
       <c r="F1545" s="6" t="inlineStr">
@@ -48962,7 +48962,7 @@
         </is>
       </c>
       <c r="G1545" s="4" t="n">
-        <v>199.57</v>
+        <v>82</v>
       </c>
     </row>
     <row r="1546">
@@ -48973,18 +48973,18 @@
       </c>
       <c r="B1546" s="6" t="inlineStr">
         <is>
-          <t>1.480,00</t>
+          <t>877,00</t>
         </is>
       </c>
       <c r="C1546" s="6" t="inlineStr"/>
       <c r="D1546" s="6" t="inlineStr">
         <is>
-          <t>SACA ARENA</t>
+          <t>ROLLO PLASTICO</t>
         </is>
       </c>
       <c r="E1546" s="6" t="inlineStr">
         <is>
-          <t>MATERIALES DE CONSTRUCCION LOS CAPITOS SL.</t>
+          <t>JUAN JOSÉ MUÑOZ ROBLES</t>
         </is>
       </c>
       <c r="F1546" s="6" t="inlineStr">
@@ -48993,7 +48993,7 @@
         </is>
       </c>
       <c r="G1546" s="4" t="n">
-        <v>192.4</v>
+        <v>72</v>
       </c>
     </row>
     <row r="1547">
@@ -49004,18 +49004,18 @@
       </c>
       <c r="B1547" s="6" t="inlineStr">
         <is>
-          <t>1.276,00</t>
+          <t>876,00</t>
         </is>
       </c>
       <c r="C1547" s="6" t="inlineStr"/>
       <c r="D1547" s="6" t="inlineStr">
         <is>
-          <t>PRESUPUESTO 616437</t>
+          <t>ROLLO PLÁSTICO</t>
         </is>
       </c>
       <c r="E1547" s="6" t="inlineStr">
         <is>
-          <t>LEROY MERLIN ESPAÑA SL</t>
+          <t>JUAN JOSÉ MUÑOZ ROBLES</t>
         </is>
       </c>
       <c r="F1547" s="6" t="inlineStr">
@@ -49024,7 +49024,7 @@
         </is>
       </c>
       <c r="G1547" s="4" t="n">
-        <v>183.24</v>
+        <v>72</v>
       </c>
     </row>
     <row r="1548">
@@ -49035,18 +49035,18 @@
       </c>
       <c r="B1548" s="6" t="inlineStr">
         <is>
-          <t>789,00</t>
+          <t>1.479,00</t>
         </is>
       </c>
       <c r="C1548" s="6" t="inlineStr"/>
       <c r="D1548" s="6" t="inlineStr">
         <is>
-          <t>DESBROCE SOLAR</t>
+          <t>GRUA</t>
         </is>
       </c>
       <c r="E1548" s="6" t="inlineStr">
         <is>
-          <t>MARCOS GALIANO POVEDA</t>
+          <t>JOSE LUIS PEREZ JAREÑO</t>
         </is>
       </c>
       <c r="F1548" s="6" t="inlineStr">
@@ -49055,7 +49055,7 @@
         </is>
       </c>
       <c r="G1548" s="4" t="n">
-        <v>180</v>
+        <v>45</v>
       </c>
     </row>
     <row r="1549">
@@ -49066,18 +49066,18 @@
       </c>
       <c r="B1549" s="6" t="inlineStr">
         <is>
-          <t>595,00</t>
+          <t>1.528,00</t>
         </is>
       </c>
       <c r="C1549" s="6" t="inlineStr"/>
       <c r="D1549" s="6" t="inlineStr">
         <is>
-          <t>VALLA MOVIL TIPO S</t>
+          <t>PINTURA/BROCHA/CEPILLO</t>
         </is>
       </c>
       <c r="E1549" s="6" t="inlineStr">
         <is>
-          <t>MATERIALES DE CONSTRUCCION LOS CAPITOS SL.</t>
+          <t>ESTABLECIMIENTOS DEMETRIO SL</t>
         </is>
       </c>
       <c r="F1549" s="6" t="inlineStr">
@@ -49086,7 +49086,7 @@
         </is>
       </c>
       <c r="G1549" s="4" t="n">
-        <v>132.98</v>
+        <v>42.56</v>
       </c>
     </row>
     <row r="1550">
@@ -49097,18 +49097,18 @@
       </c>
       <c r="B1550" s="6" t="inlineStr">
         <is>
-          <t>1.103,00</t>
+          <t>594,00</t>
         </is>
       </c>
       <c r="C1550" s="6" t="inlineStr"/>
       <c r="D1550" s="6" t="inlineStr">
         <is>
-          <t>DUMPER PINCHAZO</t>
+          <t>CADENA GALVANIZADA / CANDADO / HEMBRILLA / TACO</t>
         </is>
       </c>
       <c r="E1550" s="6" t="inlineStr">
         <is>
-          <t>CHOOSEMAK SOCIEDAD DE RESPONSABILIDAD LIMITADA</t>
+          <t>ESTABLECIMIENTOS DEMETRIO SL</t>
         </is>
       </c>
       <c r="F1550" s="6" t="inlineStr">
@@ -49117,7 +49117,7 @@
         </is>
       </c>
       <c r="G1550" s="4" t="n">
-        <v>82</v>
+        <v>29.87</v>
       </c>
     </row>
     <row r="1551">
@@ -49128,18 +49128,18 @@
       </c>
       <c r="B1551" s="6" t="inlineStr">
         <is>
-          <t>877,00</t>
+          <t>589,00</t>
         </is>
       </c>
       <c r="C1551" s="6" t="inlineStr"/>
       <c r="D1551" s="6" t="inlineStr">
         <is>
-          <t>ROLLO PLASTICO</t>
+          <t>MATERIAL</t>
         </is>
       </c>
       <c r="E1551" s="6" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ MUÑOZ ROBLES</t>
+          <t>ESTABLECIMIENTOS DEMETRIO SL</t>
         </is>
       </c>
       <c r="F1551" s="6" t="inlineStr">
@@ -49148,7 +49148,7 @@
         </is>
       </c>
       <c r="G1551" s="4" t="n">
-        <v>72</v>
+        <v>23.89</v>
       </c>
     </row>
     <row r="1552">
@@ -49159,18 +49159,18 @@
       </c>
       <c r="B1552" s="6" t="inlineStr">
         <is>
-          <t>876,00</t>
+          <t>1.108,00</t>
         </is>
       </c>
       <c r="C1552" s="6" t="inlineStr"/>
       <c r="D1552" s="6" t="inlineStr">
         <is>
-          <t>ROLLO PLÁSTICO</t>
+          <t>CANDADO</t>
         </is>
       </c>
       <c r="E1552" s="6" t="inlineStr">
         <is>
-          <t>JUAN JOSÉ MUÑOZ ROBLES</t>
+          <t>ESTABLECIMIENTOS DEMETRIO SL</t>
         </is>
       </c>
       <c r="F1552" s="6" t="inlineStr">
@@ -49179,29 +49179,29 @@
         </is>
       </c>
       <c r="G1552" s="4" t="n">
-        <v>72</v>
+        <v>12.23</v>
       </c>
     </row>
     <row r="1553">
       <c r="A1553" s="6" t="inlineStr">
         <is>
-          <t>24018 - OBRA LUC2</t>
+          <t>2600 - OBRA MURO CAMPO ARANTXA</t>
         </is>
       </c>
       <c r="B1553" s="6" t="inlineStr">
         <is>
-          <t>1.479,00</t>
+          <t>875,00</t>
         </is>
       </c>
       <c r="C1553" s="6" t="inlineStr"/>
       <c r="D1553" s="6" t="inlineStr">
         <is>
-          <t>GRUA</t>
+          <t>LEROY MERIN (PRESUPUESTO 605142)</t>
         </is>
       </c>
       <c r="E1553" s="6" t="inlineStr">
         <is>
-          <t>JOSE LUIS PEREZ JAREÑO</t>
+          <t>LEROY MERLIN ESPAÑA SL</t>
         </is>
       </c>
       <c r="F1553" s="6" t="inlineStr">
@@ -49210,29 +49210,29 @@
         </is>
       </c>
       <c r="G1553" s="4" t="n">
-        <v>45</v>
+        <v>3338.27</v>
       </c>
     </row>
     <row r="1554">
       <c r="A1554" s="6" t="inlineStr">
         <is>
-          <t>24018 - OBRA LUC2</t>
+          <t>2600 - OBRA MURO CAMPO ARANTXA</t>
         </is>
       </c>
       <c r="B1554" s="6" t="inlineStr">
         <is>
-          <t>1.528,00</t>
+          <t>914,00</t>
         </is>
       </c>
       <c r="C1554" s="6" t="inlineStr"/>
       <c r="D1554" s="6" t="inlineStr">
         <is>
-          <t>PINTURA/BROCHA/CEPILLO</t>
+          <t>PRESUPUESTO Nº 609376</t>
         </is>
       </c>
       <c r="E1554" s="6" t="inlineStr">
         <is>
-          <t>ESTABLECIMIENTOS DEMETRIO SL</t>
+          <t>LEROY MERLIN ESPAÑA SL</t>
         </is>
       </c>
       <c r="F1554" s="6" t="inlineStr">
@@ -49241,29 +49241,29 @@
         </is>
       </c>
       <c r="G1554" s="4" t="n">
-        <v>42.56</v>
+        <v>477.49</v>
       </c>
     </row>
     <row r="1555">
       <c r="A1555" s="6" t="inlineStr">
         <is>
-          <t>24018 - OBRA LUC2</t>
+          <t>2600 - OBRA MURO CAMPO ARANTXA</t>
         </is>
       </c>
       <c r="B1555" s="6" t="inlineStr">
         <is>
-          <t>594,00</t>
+          <t>918,00</t>
         </is>
       </c>
       <c r="C1555" s="6" t="inlineStr"/>
       <c r="D1555" s="6" t="inlineStr">
         <is>
-          <t>CADENA GALVANIZADA / CANDADO / HEMBRILLA / TACO</t>
+          <t>PRESUPUESTO Nº 607423-2</t>
         </is>
       </c>
       <c r="E1555" s="6" t="inlineStr">
         <is>
-          <t>ESTABLECIMIENTOS DEMETRIO SL</t>
+          <t>LEROY MERLIN ESPAÑA SL</t>
         </is>
       </c>
       <c r="F1555" s="6" t="inlineStr">
@@ -49272,29 +49272,29 @@
         </is>
       </c>
       <c r="G1555" s="4" t="n">
-        <v>29.87</v>
+        <v>414.57</v>
       </c>
     </row>
     <row r="1556">
       <c r="A1556" s="6" t="inlineStr">
         <is>
-          <t>24018 - OBRA LUC2</t>
+          <t>26001 - SANTA ROSA</t>
         </is>
       </c>
       <c r="B1556" s="6" t="inlineStr">
         <is>
-          <t>589,00</t>
+          <t>1.121,00</t>
         </is>
       </c>
       <c r="C1556" s="6" t="inlineStr"/>
       <c r="D1556" s="6" t="inlineStr">
         <is>
-          <t>MATERIAL</t>
+          <t>PLADUR</t>
         </is>
       </c>
       <c r="E1556" s="6" t="inlineStr">
         <is>
-          <t>ESTABLECIMIENTOS DEMETRIO SL</t>
+          <t>FRANCISCO JOSE BERMEJO ROSA</t>
         </is>
       </c>
       <c r="F1556" s="6" t="inlineStr">
@@ -49303,29 +49303,29 @@
         </is>
       </c>
       <c r="G1556" s="4" t="n">
-        <v>23.89</v>
+        <v>2940</v>
       </c>
     </row>
     <row r="1557">
       <c r="A1557" s="6" t="inlineStr">
         <is>
-          <t>24018 - OBRA LUC2</t>
+          <t>26001 - SANTA ROSA</t>
         </is>
       </c>
       <c r="B1557" s="6" t="inlineStr">
         <is>
-          <t>1.108,00</t>
+          <t>610,00</t>
         </is>
       </c>
       <c r="C1557" s="6" t="inlineStr"/>
       <c r="D1557" s="6" t="inlineStr">
         <is>
-          <t>CANDADO</t>
+          <t>INSTALACIÓN ELÉCTRICA EN VIVIENDA Y BOLETÍN</t>
         </is>
       </c>
       <c r="E1557" s="6" t="inlineStr">
         <is>
-          <t>ESTABLECIMIENTOS DEMETRIO SL</t>
+          <t>MOVE2GO SL.</t>
         </is>
       </c>
       <c r="F1557" s="6" t="inlineStr">
@@ -49334,29 +49334,29 @@
         </is>
       </c>
       <c r="G1557" s="4" t="n">
-        <v>12.23</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="1558">
       <c r="A1558" s="6" t="inlineStr">
         <is>
-          <t>2600 - OBRA MURO CAMPO ARANTXA</t>
+          <t>26001 - SANTA ROSA</t>
         </is>
       </c>
       <c r="B1558" s="6" t="inlineStr">
         <is>
-          <t>875,00</t>
+          <t>1.267,00</t>
         </is>
       </c>
       <c r="C1558" s="6" t="inlineStr"/>
       <c r="D1558" s="6" t="inlineStr">
         <is>
-          <t>LEROY MERIN (PRESUPUESTO 605142)</t>
+          <t>COLOCACIÓN TARIMA</t>
         </is>
       </c>
       <c r="E1558" s="6" t="inlineStr">
         <is>
-          <t>LEROY MERLIN ESPAÑA SL</t>
+          <t>OSCAR DAINEL NUÑEZ BOBADILLA</t>
         </is>
       </c>
       <c r="F1558" s="6" t="inlineStr">
@@ -49365,29 +49365,29 @@
         </is>
       </c>
       <c r="G1558" s="4" t="n">
-        <v>3338.27</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="1559">
       <c r="A1559" s="6" t="inlineStr">
         <is>
-          <t>2600 - OBRA MURO CAMPO ARANTXA</t>
+          <t>26001 - SANTA ROSA</t>
         </is>
       </c>
       <c r="B1559" s="6" t="inlineStr">
         <is>
-          <t>914,00</t>
+          <t>1.178,00</t>
         </is>
       </c>
       <c r="C1559" s="6" t="inlineStr"/>
       <c r="D1559" s="6" t="inlineStr">
         <is>
-          <t>PRESUPUESTO Nº 609376</t>
+          <t>Mano de Obra Tarima #tarima, puertas</t>
         </is>
       </c>
       <c r="E1559" s="6" t="inlineStr">
         <is>
-          <t>LEROY MERLIN ESPAÑA SL</t>
+          <t>ION NITU</t>
         </is>
       </c>
       <c r="F1559" s="6" t="inlineStr">
@@ -49396,29 +49396,29 @@
         </is>
       </c>
       <c r="G1559" s="4" t="n">
-        <v>477.49</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="1560">
       <c r="A1560" s="6" t="inlineStr">
         <is>
-          <t>2600 - OBRA MURO CAMPO ARANTXA</t>
+          <t>26001 - SANTA ROSA</t>
         </is>
       </c>
       <c r="B1560" s="6" t="inlineStr">
         <is>
-          <t>918,00</t>
+          <t>598,00</t>
         </is>
       </c>
       <c r="C1560" s="6" t="inlineStr"/>
       <c r="D1560" s="6" t="inlineStr">
         <is>
-          <t>PRESUPUESTO Nº 607423-2</t>
+          <t>MASILLA PARA ALISAR</t>
         </is>
       </c>
       <c r="E1560" s="6" t="inlineStr">
         <is>
-          <t>LEROY MERLIN ESPAÑA SL</t>
+          <t>DECOBRIC SANZ SL</t>
         </is>
       </c>
       <c r="F1560" s="6" t="inlineStr">
@@ -49427,7 +49427,7 @@
         </is>
       </c>
       <c r="G1560" s="4" t="n">
-        <v>414.57</v>
+        <v>726</v>
       </c>
     </row>
     <row r="1561">
@@ -49438,18 +49438,18 @@
       </c>
       <c r="B1561" s="6" t="inlineStr">
         <is>
-          <t>1.121,00</t>
+          <t>1.180,00</t>
         </is>
       </c>
       <c r="C1561" s="6" t="inlineStr"/>
       <c r="D1561" s="6" t="inlineStr">
         <is>
-          <t>PLADUR</t>
+          <t>PINTURA</t>
         </is>
       </c>
       <c r="E1561" s="6" t="inlineStr">
         <is>
-          <t>FRANCISCO JOSE BERMEJO ROSA</t>
+          <t>DECOBRIC SANZ SL</t>
         </is>
       </c>
       <c r="F1561" s="6" t="inlineStr">
@@ -49458,7 +49458,7 @@
         </is>
       </c>
       <c r="G1561" s="4" t="n">
-        <v>2940</v>
+        <v>470.35</v>
       </c>
     </row>
     <row r="1562">
@@ -49469,18 +49469,18 @@
       </c>
       <c r="B1562" s="6" t="inlineStr">
         <is>
-          <t>610,00</t>
+          <t>619,00</t>
         </is>
       </c>
       <c r="C1562" s="6" t="inlineStr"/>
       <c r="D1562" s="6" t="inlineStr">
         <is>
-          <t>INSTALACIÓN ELÉCTRICA EN VIVIENDA Y BOLETÍN</t>
+          <t>CONTENEDORES</t>
         </is>
       </c>
       <c r="E1562" s="6" t="inlineStr">
         <is>
-          <t>MOVE2GO SL.</t>
+          <t>CONTENEDORES REUNIDOS SL</t>
         </is>
       </c>
       <c r="F1562" s="6" t="inlineStr">
@@ -49489,7 +49489,7 @@
         </is>
       </c>
       <c r="G1562" s="4" t="n">
-        <v>1488</v>
+        <v>435</v>
       </c>
     </row>
     <row r="1563">
@@ -49500,18 +49500,18 @@
       </c>
       <c r="B1563" s="6" t="inlineStr">
         <is>
-          <t>1.267,00</t>
+          <t>879,00</t>
         </is>
       </c>
       <c r="C1563" s="6" t="inlineStr"/>
       <c r="D1563" s="6" t="inlineStr">
         <is>
-          <t>COLOCACIÓN TARIMA</t>
+          <t>LEROY MERLIN (PRESUPUESTO 606525)</t>
         </is>
       </c>
       <c r="E1563" s="6" t="inlineStr">
         <is>
-          <t>OSCAR DAINEL NUÑEZ BOBADILLA</t>
+          <t>LEROY MERLIN ESPAÑA SL</t>
         </is>
       </c>
       <c r="F1563" s="6" t="inlineStr">
@@ -49520,7 +49520,7 @@
         </is>
       </c>
       <c r="G1563" s="4" t="n">
-        <v>1180</v>
+        <v>345.13</v>
       </c>
     </row>
     <row r="1564">
@@ -49531,18 +49531,18 @@
       </c>
       <c r="B1564" s="6" t="inlineStr">
         <is>
-          <t>1.178,00</t>
+          <t>615,00</t>
         </is>
       </c>
       <c r="C1564" s="6" t="inlineStr"/>
       <c r="D1564" s="6" t="inlineStr">
         <is>
-          <t>Mano de Obra Tarima #tarima, puertas</t>
+          <t>MATERIAL OBRA</t>
         </is>
       </c>
       <c r="E1564" s="6" t="inlineStr">
         <is>
-          <t>ION NITU</t>
+          <t>BRICOLAJE BRICOMAN SLU</t>
         </is>
       </c>
       <c r="F1564" s="6" t="inlineStr">
@@ -49551,7 +49551,7 @@
         </is>
       </c>
       <c r="G1564" s="4" t="n">
-        <v>1080</v>
+        <v>179.86</v>
       </c>
     </row>
     <row r="1565">
@@ -49562,18 +49562,18 @@
       </c>
       <c r="B1565" s="6" t="inlineStr">
         <is>
-          <t>598,00</t>
+          <t>603,00</t>
         </is>
       </c>
       <c r="C1565" s="6" t="inlineStr"/>
       <c r="D1565" s="6" t="inlineStr">
         <is>
-          <t>MASILLA PARA ALISAR</t>
+          <t>PREMARCOS</t>
         </is>
       </c>
       <c r="E1565" s="6" t="inlineStr">
         <is>
-          <t>DECOBRIC SANZ SL</t>
+          <t>CARPINTERIA EBANISTERIA BAMBU SL.</t>
         </is>
       </c>
       <c r="F1565" s="6" t="inlineStr">
@@ -49582,7 +49582,7 @@
         </is>
       </c>
       <c r="G1565" s="4" t="n">
-        <v>726</v>
+        <v>160</v>
       </c>
     </row>
     <row r="1566">
@@ -49593,18 +49593,18 @@
       </c>
       <c r="B1566" s="6" t="inlineStr">
         <is>
-          <t>1.180,00</t>
+          <t>840,00</t>
         </is>
       </c>
       <c r="C1566" s="6" t="inlineStr"/>
       <c r="D1566" s="6" t="inlineStr">
         <is>
-          <t>PINTURA</t>
+          <t>PLATO DUCHA (MEJORA + 20%)</t>
         </is>
       </c>
       <c r="E1566" s="6" t="inlineStr">
         <is>
-          <t>DECOBRIC SANZ SL</t>
+          <t>LEROY MERLIN ESPAÑA SL</t>
         </is>
       </c>
       <c r="F1566" s="6" t="inlineStr">
@@ -49613,7 +49613,7 @@
         </is>
       </c>
       <c r="G1566" s="4" t="n">
-        <v>470.35</v>
+        <v>156.16</v>
       </c>
     </row>
     <row r="1567">
@@ -49624,7 +49624,7 @@
       </c>
       <c r="B1567" s="6" t="inlineStr">
         <is>
-          <t>619,00</t>
+          <t>1.116,00</t>
         </is>
       </c>
       <c r="C1567" s="6" t="inlineStr"/>
@@ -49644,7 +49644,7 @@
         </is>
       </c>
       <c r="G1567" s="4" t="n">
-        <v>435</v>
+        <v>145</v>
       </c>
     </row>
     <row r="1568">
@@ -49655,18 +49655,18 @@
       </c>
       <c r="B1568" s="6" t="inlineStr">
         <is>
-          <t>879,00</t>
+          <t>1.135,00</t>
         </is>
       </c>
       <c r="C1568" s="6" t="inlineStr"/>
       <c r="D1568" s="6" t="inlineStr">
         <is>
-          <t>LEROY MERLIN (PRESUPUESTO 606525)</t>
+          <t>MATERIAL OBRA</t>
         </is>
       </c>
       <c r="E1568" s="6" t="inlineStr">
         <is>
-          <t>LEROY MERLIN ESPAÑA SL</t>
+          <t>BRICOLAJE BRICOMAN SLU</t>
         </is>
       </c>
       <c r="F1568" s="6" t="inlineStr">
@@ -49675,7 +49675,7 @@
         </is>
       </c>
       <c r="G1568" s="4" t="n">
-        <v>345.13</v>
+        <v>86.63</v>
       </c>
     </row>
     <row r="1569">
@@ -49686,18 +49686,18 @@
       </c>
       <c r="B1569" s="6" t="inlineStr">
         <is>
-          <t>615,00</t>
+          <t>1.223,00</t>
         </is>
       </c>
       <c r="C1569" s="6" t="inlineStr"/>
       <c r="D1569" s="6" t="inlineStr">
         <is>
-          <t>MATERIAL OBRA</t>
+          <t>PINTURA</t>
         </is>
       </c>
       <c r="E1569" s="6" t="inlineStr">
         <is>
-          <t>BRICOLAJE BRICOMAN SLU</t>
+          <t>DECOBRIC SANZ SL</t>
         </is>
       </c>
       <c r="F1569" s="6" t="inlineStr">
@@ -49706,7 +49706,7 @@
         </is>
       </c>
       <c r="G1569" s="4" t="n">
-        <v>179.86</v>
+        <v>76.5</v>
       </c>
     </row>
     <row r="1570">
@@ -49717,18 +49717,18 @@
       </c>
       <c r="B1570" s="6" t="inlineStr">
         <is>
-          <t>603,00</t>
+          <t>1.155,00</t>
         </is>
       </c>
       <c r="C1570" s="6" t="inlineStr"/>
       <c r="D1570" s="6" t="inlineStr">
         <is>
-          <t>PREMARCOS</t>
+          <t>ARENA MEZCLA / YESO CONTROL PLACO / WEBERCOL FLEX DUO / # ALBAÑILERIA - MATERIAL</t>
         </is>
       </c>
       <c r="E1570" s="6" t="inlineStr">
         <is>
-          <t>CARPINTERIA EBANISTERIA BAMBU SL.</t>
+          <t>BRICOLAJE BRICOMAN SLU</t>
         </is>
       </c>
       <c r="F1570" s="6" t="inlineStr">
@@ -49737,7 +49737,7 @@
         </is>
       </c>
       <c r="G1570" s="4" t="n">
-        <v>160</v>
+        <v>72.48</v>
       </c>
     </row>
     <row r="1571">
@@ -49748,27 +49748,23 @@
       </c>
       <c r="B1571" s="6" t="inlineStr">
         <is>
-          <t>840,00</t>
+          <t>597,00</t>
         </is>
       </c>
       <c r="C1571" s="6" t="inlineStr"/>
       <c r="D1571" s="6" t="inlineStr">
         <is>
-          <t>PLATO DUCHA (MEJORA + 20%)</t>
-        </is>
-      </c>
-      <c r="E1571" s="6" t="inlineStr">
-        <is>
-          <t>LEROY MERLIN ESPAÑA SL</t>
-        </is>
-      </c>
+          <t>DICOS ABRANET 225mm</t>
+        </is>
+      </c>
+      <c r="E1571" s="6" t="inlineStr"/>
       <c r="F1571" s="6" t="inlineStr">
         <is>
           <t>IMPUTADO</t>
         </is>
       </c>
       <c r="G1571" s="4" t="n">
-        <v>156.16</v>
+        <v>71.78</v>
       </c>
     </row>
     <row r="1572">
@@ -49779,18 +49775,18 @@
       </c>
       <c r="B1572" s="6" t="inlineStr">
         <is>
-          <t>1.116,00</t>
+          <t>1.212,00</t>
         </is>
       </c>
       <c r="C1572" s="6" t="inlineStr"/>
       <c r="D1572" s="6" t="inlineStr">
         <is>
-          <t>CONTENEDORES</t>
+          <t>PINTURA</t>
         </is>
       </c>
       <c r="E1572" s="6" t="inlineStr">
         <is>
-          <t>CONTENEDORES REUNIDOS SL</t>
+          <t>DECOBRIC SANZ SL</t>
         </is>
       </c>
       <c r="F1572" s="6" t="inlineStr">
@@ -49799,7 +49795,7 @@
         </is>
       </c>
       <c r="G1572" s="4" t="n">
-        <v>145</v>
+        <v>60.33</v>
       </c>
     </row>
     <row r="1573">
@@ -49810,18 +49806,18 @@
       </c>
       <c r="B1573" s="6" t="inlineStr">
         <is>
-          <t>1.135,00</t>
+          <t>841,00</t>
         </is>
       </c>
       <c r="C1573" s="6" t="inlineStr"/>
       <c r="D1573" s="6" t="inlineStr">
         <is>
-          <t>MATERIAL OBRA</t>
+          <t>CERROJO SEGURIDAD (MEJORA + 20%) ENEL CERROJO</t>
         </is>
       </c>
       <c r="E1573" s="6" t="inlineStr">
         <is>
-          <t>BRICOLAJE BRICOMAN SLU</t>
+          <t>FERRETERIA SANTIAGO EL MAYOR</t>
         </is>
       </c>
       <c r="F1573" s="6" t="inlineStr">
@@ -49830,7 +49826,7 @@
         </is>
       </c>
       <c r="G1573" s="4" t="n">
-        <v>86.63</v>
+        <v>59.13</v>
       </c>
     </row>
     <row r="1574">
@@ -49841,18 +49837,18 @@
       </c>
       <c r="B1574" s="6" t="inlineStr">
         <is>
-          <t>1.223,00</t>
+          <t>614,00</t>
         </is>
       </c>
       <c r="C1574" s="6" t="inlineStr"/>
       <c r="D1574" s="6" t="inlineStr">
         <is>
-          <t>PINTURA</t>
+          <t>MATERIAL OBRA</t>
         </is>
       </c>
       <c r="E1574" s="6" t="inlineStr">
         <is>
-          <t>DECOBRIC SANZ SL</t>
+          <t>BRICOLAJE BRICOMAN SLU</t>
         </is>
       </c>
       <c r="F1574" s="6" t="inlineStr">
@@ -49861,7 +49857,7 @@
         </is>
       </c>
       <c r="G1574" s="4" t="n">
-        <v>76.5</v>
+        <v>53.17</v>
       </c>
     </row>
     <row r="1575">
@@ -49872,13 +49868,13 @@
       </c>
       <c r="B1575" s="6" t="inlineStr">
         <is>
-          <t>1.155,00</t>
+          <t>814,00</t>
         </is>
       </c>
       <c r="C1575" s="6" t="inlineStr"/>
       <c r="D1575" s="6" t="inlineStr">
         <is>
-          <t>ARENA MEZCLA / YESO CONTROL PLACO / WEBERCOL FLEX DUO / # ALBAÑILERIA - MATERIAL</t>
+          <t>GRAVA / ARENA BCO / CEMENTO / YEO CONTROL #ALBAÑILERIA - MATERIAL</t>
         </is>
       </c>
       <c r="E1575" s="6" t="inlineStr">
@@ -49892,7 +49888,7 @@
         </is>
       </c>
       <c r="G1575" s="4" t="n">
-        <v>72.48</v>
+        <v>51.94</v>
       </c>
     </row>
     <row r="1576">
@@ -49903,23 +49899,27 @@
       </c>
       <c r="B1576" s="6" t="inlineStr">
         <is>
-          <t>597,00</t>
+          <t>1.248,00</t>
         </is>
       </c>
       <c r="C1576" s="6" t="inlineStr"/>
       <c r="D1576" s="6" t="inlineStr">
         <is>
-          <t>DICOS ABRANET 225mm</t>
-        </is>
-      </c>
-      <c r="E1576" s="6" t="inlineStr"/>
+          <t>ARREGLO PERSINAA</t>
+        </is>
+      </c>
+      <c r="E1576" s="6" t="inlineStr">
+        <is>
+          <t>TABLEROS Y PUERTAS MORENO SL</t>
+        </is>
+      </c>
       <c r="F1576" s="6" t="inlineStr">
         <is>
           <t>IMPUTADO</t>
         </is>
       </c>
       <c r="G1576" s="4" t="n">
-        <v>71.78</v>
+        <v>45.73</v>
       </c>
     </row>
     <row r="1577">
@@ -49930,18 +49930,18 @@
       </c>
       <c r="B1577" s="6" t="inlineStr">
         <is>
-          <t>1.212,00</t>
+          <t>1.508,00</t>
         </is>
       </c>
       <c r="C1577" s="6" t="inlineStr"/>
       <c r="D1577" s="6" t="inlineStr">
         <is>
-          <t>PINTURA</t>
+          <t>MATERIAL OBRA</t>
         </is>
       </c>
       <c r="E1577" s="6" t="inlineStr">
         <is>
-          <t>DECOBRIC SANZ SL</t>
+          <t>LEROY MERLIN ESPAÑA SL</t>
         </is>
       </c>
       <c r="F1577" s="6" t="inlineStr">
@@ -49950,7 +49950,7 @@
         </is>
       </c>
       <c r="G1577" s="4" t="n">
-        <v>60.33</v>
+        <v>45.32</v>
       </c>
     </row>
     <row r="1578">
@@ -49961,18 +49961,18 @@
       </c>
       <c r="B1578" s="6" t="inlineStr">
         <is>
-          <t>841,00</t>
+          <t>1.099,00</t>
         </is>
       </c>
       <c r="C1578" s="6" t="inlineStr"/>
       <c r="D1578" s="6" t="inlineStr">
         <is>
-          <t>CERROJO SEGURIDAD (MEJORA + 20%) ENEL CERROJO</t>
+          <t>TUBO EXTRACCIÓN</t>
         </is>
       </c>
       <c r="E1578" s="6" t="inlineStr">
         <is>
-          <t>FERRETERIA SANTIAGO EL MAYOR</t>
+          <t>LEROY MERLIN ESPAÑA SL</t>
         </is>
       </c>
       <c r="F1578" s="6" t="inlineStr">
@@ -49981,7 +49981,7 @@
         </is>
       </c>
       <c r="G1578" s="4" t="n">
-        <v>59.13</v>
+        <v>37.84</v>
       </c>
     </row>
     <row r="1579">
@@ -49992,7 +49992,7 @@
       </c>
       <c r="B1579" s="6" t="inlineStr">
         <is>
-          <t>614,00</t>
+          <t>1.221,00</t>
         </is>
       </c>
       <c r="C1579" s="6" t="inlineStr"/>
@@ -50003,7 +50003,7 @@
       </c>
       <c r="E1579" s="6" t="inlineStr">
         <is>
-          <t>BRICOLAJE BRICOMAN SLU</t>
+          <t>FERRETERIA SANTIAGO EL MAYOR</t>
         </is>
       </c>
       <c r="F1579" s="6" t="inlineStr">
@@ -50012,7 +50012,7 @@
         </is>
       </c>
       <c r="G1579" s="4" t="n">
-        <v>53.17</v>
+        <v>34.46</v>
       </c>
     </row>
     <row r="1580">
@@ -50023,18 +50023,18 @@
       </c>
       <c r="B1580" s="6" t="inlineStr">
         <is>
-          <t>814,00</t>
+          <t>1.229,00</t>
         </is>
       </c>
       <c r="C1580" s="6" t="inlineStr"/>
       <c r="D1580" s="6" t="inlineStr">
         <is>
-          <t>GRAVA / ARENA BCO / CEMENTO / YEO CONTROL #ALBAÑILERIA - MATERIAL</t>
+          <t>MATERIAL OBRA #mejora</t>
         </is>
       </c>
       <c r="E1580" s="6" t="inlineStr">
         <is>
-          <t>BRICOLAJE BRICOMAN SLU</t>
+          <t>LEROY MERLIN ESPAÑA SL</t>
         </is>
       </c>
       <c r="F1580" s="6" t="inlineStr">
@@ -50043,7 +50043,7 @@
         </is>
       </c>
       <c r="G1580" s="4" t="n">
-        <v>51.94</v>
+        <v>33.12</v>
       </c>
     </row>
     <row r="1581">
@@ -50054,18 +50054,18 @@
       </c>
       <c r="B1581" s="6" t="inlineStr">
         <is>
-          <t>1.248,00</t>
+          <t>1.213,00</t>
         </is>
       </c>
       <c r="C1581" s="6" t="inlineStr"/>
       <c r="D1581" s="6" t="inlineStr">
         <is>
-          <t>ARREGLO PERSINAA</t>
+          <t>MORAFOND-LIMPIEZA SALITRE  OXIDOO #mejora</t>
         </is>
       </c>
       <c r="E1581" s="6" t="inlineStr">
         <is>
-          <t>TABLEROS Y PUERTAS MORENO SL</t>
+          <t>DECOBRIC SANZ SL</t>
         </is>
       </c>
       <c r="F1581" s="6" t="inlineStr">
@@ -50074,7 +50074,7 @@
         </is>
       </c>
       <c r="G1581" s="4" t="n">
-        <v>45.73</v>
+        <v>21.66</v>
       </c>
     </row>
     <row r="1582">
@@ -50085,18 +50085,18 @@
       </c>
       <c r="B1582" s="6" t="inlineStr">
         <is>
-          <t>1.508,00</t>
+          <t>1.263,00</t>
         </is>
       </c>
       <c r="C1582" s="6" t="inlineStr"/>
       <c r="D1582" s="6" t="inlineStr">
         <is>
-          <t>MATERIAL OBRA</t>
+          <t>PISTOLA SILICONA, BOCA EXTRACCION</t>
         </is>
       </c>
       <c r="E1582" s="6" t="inlineStr">
         <is>
-          <t>LEROY MERLIN ESPAÑA SL</t>
+          <t>BRICOLAJE BRICOMAN SLU</t>
         </is>
       </c>
       <c r="F1582" s="6" t="inlineStr">
@@ -50105,7 +50105,7 @@
         </is>
       </c>
       <c r="G1582" s="4" t="n">
-        <v>45.32</v>
+        <v>20.46</v>
       </c>
     </row>
     <row r="1583">
@@ -50116,13 +50116,13 @@
       </c>
       <c r="B1583" s="6" t="inlineStr">
         <is>
-          <t>1.099,00</t>
+          <t>1.269,00</t>
         </is>
       </c>
       <c r="C1583" s="6" t="inlineStr"/>
       <c r="D1583" s="6" t="inlineStr">
         <is>
-          <t>TUBO EXTRACCIÓN</t>
+          <t>MATERIAL</t>
         </is>
       </c>
       <c r="E1583" s="6" t="inlineStr">
@@ -50136,7 +50136,7 @@
         </is>
       </c>
       <c r="G1583" s="4" t="n">
-        <v>37.84</v>
+        <v>17.83</v>
       </c>
     </row>
     <row r="1584">
@@ -50147,18 +50147,18 @@
       </c>
       <c r="B1584" s="6" t="inlineStr">
         <is>
-          <t>1.221,00</t>
+          <t>1.224,00</t>
         </is>
       </c>
       <c r="C1584" s="6" t="inlineStr"/>
       <c r="D1584" s="6" t="inlineStr">
         <is>
-          <t>MATERIAL OBRA</t>
+          <t>PINTURA</t>
         </is>
       </c>
       <c r="E1584" s="6" t="inlineStr">
         <is>
-          <t>FERRETERIA SANTIAGO EL MAYOR</t>
+          <t>DECOBRIC SANZ SL</t>
         </is>
       </c>
       <c r="F1584" s="6" t="inlineStr">
@@ -50167,7 +50167,7 @@
         </is>
       </c>
       <c r="G1584" s="4" t="n">
-        <v>34.46</v>
+        <v>17.83</v>
       </c>
     </row>
     <row r="1585">
@@ -50178,13 +50178,13 @@
       </c>
       <c r="B1585" s="6" t="inlineStr">
         <is>
-          <t>1.229,00</t>
+          <t>1.204,00</t>
         </is>
       </c>
       <c r="C1585" s="6" t="inlineStr"/>
       <c r="D1585" s="6" t="inlineStr">
         <is>
-          <t>MATERIAL OBRA #mejora</t>
+          <t>ADH ACRILICO - ESPUMA TEJAS #mejora</t>
         </is>
       </c>
       <c r="E1585" s="6" t="inlineStr">
@@ -50198,7 +50198,7 @@
         </is>
       </c>
       <c r="G1585" s="4" t="n">
-        <v>33.12</v>
+        <v>15.29</v>
       </c>
     </row>
     <row r="1586">
@@ -50209,18 +50209,18 @@
       </c>
       <c r="B1586" s="6" t="inlineStr">
         <is>
-          <t>1.213,00</t>
+          <t>812,00</t>
         </is>
       </c>
       <c r="C1586" s="6" t="inlineStr"/>
       <c r="D1586" s="6" t="inlineStr">
         <is>
-          <t>MORAFOND-LIMPIEZA SALITRE  OXIDOO #mejora</t>
+          <t>TUVO PVC VARIOS #ALBAÑILERIA - MATERIAL</t>
         </is>
       </c>
       <c r="E1586" s="6" t="inlineStr">
         <is>
-          <t>DECOBRIC SANZ SL</t>
+          <t>BRICOLAJE BRICOMAN SLU</t>
         </is>
       </c>
       <c r="F1586" s="6" t="inlineStr">
@@ -50229,7 +50229,7 @@
         </is>
       </c>
       <c r="G1586" s="4" t="n">
-        <v>21.66</v>
+        <v>14.2</v>
       </c>
     </row>
     <row r="1587">
@@ -50240,18 +50240,18 @@
       </c>
       <c r="B1587" s="6" t="inlineStr">
         <is>
-          <t>1.263,00</t>
+          <t>1.247,00</t>
         </is>
       </c>
       <c r="C1587" s="6" t="inlineStr"/>
       <c r="D1587" s="6" t="inlineStr">
         <is>
-          <t>PISTOLA SILICONA, BOCA EXTRACCION</t>
+          <t>MATERIAL PERSIANA #mejora pintura</t>
         </is>
       </c>
       <c r="E1587" s="6" t="inlineStr">
         <is>
-          <t>BRICOLAJE BRICOMAN SLU</t>
+          <t>FERRETERIA SANTIAGO EL MAYOR</t>
         </is>
       </c>
       <c r="F1587" s="6" t="inlineStr">
@@ -50260,29 +50260,29 @@
         </is>
       </c>
       <c r="G1587" s="4" t="n">
-        <v>20.46</v>
+        <v>8.550000000000001</v>
       </c>
     </row>
     <row r="1588">
       <c r="A1588" s="6" t="inlineStr">
         <is>
-          <t>26001 - SANTA ROSA</t>
+          <t>26002 - GARAJE MURCIA</t>
         </is>
       </c>
       <c r="B1588" s="6" t="inlineStr">
         <is>
-          <t>1.269,00</t>
+          <t>1.173,00</t>
         </is>
       </c>
       <c r="C1588" s="6" t="inlineStr"/>
       <c r="D1588" s="6" t="inlineStr">
         <is>
-          <t>MATERIAL</t>
+          <t>INTALACIÓN COMPLETA DE ELECTRICIDAD EN GARAJE</t>
         </is>
       </c>
       <c r="E1588" s="6" t="inlineStr">
         <is>
-          <t>LEROY MERLIN ESPAÑA SL</t>
+          <t>MOVE2GO SL.</t>
         </is>
       </c>
       <c r="F1588" s="6" t="inlineStr">
@@ -50291,29 +50291,29 @@
         </is>
       </c>
       <c r="G1588" s="4" t="n">
-        <v>17.83</v>
+        <v>1087.5</v>
       </c>
     </row>
     <row r="1589">
       <c r="A1589" s="6" t="inlineStr">
         <is>
-          <t>26001 - SANTA ROSA</t>
+          <t>26002 - GARAJE MURCIA</t>
         </is>
       </c>
       <c r="B1589" s="6" t="inlineStr">
         <is>
-          <t>1.224,00</t>
+          <t>851,00</t>
         </is>
       </c>
       <c r="C1589" s="6" t="inlineStr"/>
       <c r="D1589" s="6" t="inlineStr">
         <is>
-          <t>PINTURA</t>
+          <t>INTALACIÓN COMPLETA DE ELECTRICIDAD EN GARAJE</t>
         </is>
       </c>
       <c r="E1589" s="6" t="inlineStr">
         <is>
-          <t>DECOBRIC SANZ SL</t>
+          <t>MOVE2GO SL.</t>
         </is>
       </c>
       <c r="F1589" s="6" t="inlineStr">
@@ -50322,24 +50322,24 @@
         </is>
       </c>
       <c r="G1589" s="4" t="n">
-        <v>17.83</v>
+        <v>1087.5</v>
       </c>
     </row>
     <row r="1590">
       <c r="A1590" s="6" t="inlineStr">
         <is>
-          <t>26001 - SANTA ROSA</t>
+          <t>26002 - GARAJE MURCIA</t>
         </is>
       </c>
       <c r="B1590" s="6" t="inlineStr">
         <is>
-          <t>1.204,00</t>
+          <t>874,00</t>
         </is>
       </c>
       <c r="C1590" s="6" t="inlineStr"/>
       <c r="D1590" s="6" t="inlineStr">
         <is>
-          <t>ADH ACRILICO - ESPUMA TEJAS #mejora</t>
+          <t>LEROY MERLIN (PRESUPUESTO 603119) FOTO EN DOCUMENTOS</t>
         </is>
       </c>
       <c r="E1590" s="6" t="inlineStr">
@@ -50353,29 +50353,29 @@
         </is>
       </c>
       <c r="G1590" s="4" t="n">
-        <v>15.29</v>
+        <v>469.96</v>
       </c>
     </row>
     <row r="1591">
       <c r="A1591" s="6" t="inlineStr">
         <is>
-          <t>26001 - SANTA ROSA</t>
+          <t>26002 - GARAJE MURCIA</t>
         </is>
       </c>
       <c r="B1591" s="6" t="inlineStr">
         <is>
-          <t>812,00</t>
+          <t>853,00</t>
         </is>
       </c>
       <c r="C1591" s="6" t="inlineStr"/>
       <c r="D1591" s="6" t="inlineStr">
         <is>
-          <t>TUVO PVC VARIOS #ALBAÑILERIA - MATERIAL</t>
+          <t>LEROY MERLIN (PRESUPUESTO 602161) FOTO EN DOCUMENTOS</t>
         </is>
       </c>
       <c r="E1591" s="6" t="inlineStr">
         <is>
-          <t>BRICOLAJE BRICOMAN SLU</t>
+          <t>LEROY MERLIN ESPAÑA SL</t>
         </is>
       </c>
       <c r="F1591" s="6" t="inlineStr">
@@ -50384,29 +50384,29 @@
         </is>
       </c>
       <c r="G1591" s="4" t="n">
-        <v>14.2</v>
+        <v>352.76</v>
       </c>
     </row>
     <row r="1592">
       <c r="A1592" s="6" t="inlineStr">
         <is>
-          <t>26001 - SANTA ROSA</t>
+          <t>26002 - GARAJE MURCIA</t>
         </is>
       </c>
       <c r="B1592" s="6" t="inlineStr">
         <is>
-          <t>1.247,00</t>
+          <t>852,00</t>
         </is>
       </c>
       <c r="C1592" s="6" t="inlineStr"/>
       <c r="D1592" s="6" t="inlineStr">
         <is>
-          <t>MATERIAL PERSIANA #mejora pintura</t>
+          <t>LEROY MERLIN (DUPLICADO PRESUPUESTO 601689) FOTO EN DOCUMENTOS</t>
         </is>
       </c>
       <c r="E1592" s="6" t="inlineStr">
         <is>
-          <t>FERRETERIA SANTIAGO EL MAYOR</t>
+          <t>LEROY MERLIN ESPAÑA SL</t>
         </is>
       </c>
       <c r="F1592" s="6" t="inlineStr">
@@ -50415,7 +50415,7 @@
         </is>
       </c>
       <c r="G1592" s="4" t="n">
-        <v>8.550000000000001</v>
+        <v>352.76</v>
       </c>
     </row>
     <row r="1593">

--- a/ECO_STRUCT_Datos.xlsx
+++ b/ECO_STRUCT_Datos.xlsx
@@ -1800,7 +1800,7 @@
         </is>
       </c>
       <c r="C21" s="4" t="n">
-        <v>15050.98</v>
+        <v>20972.59</v>
       </c>
       <c r="D21" s="6">
         <f>C21/C24</f>

--- a/ECO_STRUCT_Datos.xlsx
+++ b/ECO_STRUCT_Datos.xlsx
@@ -2096,7 +2096,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>24017 - GARAJE MURCIA</t>
+          <t>26002 - GARAJE MURCIA</t>
         </is>
       </c>
       <c r="B5" s="6" t="n">
